--- a/labs/4.lab/4.lab.xlsx
+++ b/labs/4.lab/4.lab.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rod/Documents/ehu/dt/labs/4.lab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A720EF-7118-5945-9898-1F3F0BA90DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EFC2E4-C239-F84F-BAE6-AF1ED79007AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="21440" windowHeight="22400" xr2:uid="{B4FD20D9-57F3-4747-AA10-0A42781B4A42}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{B4FD20D9-57F3-4747-AA10-0A42781B4A42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="67">
   <si>
     <t>a</t>
   </si>
@@ -370,6 +370,27 @@
   <si>
     <t>для мультиплексора 16/1</t>
   </si>
+  <si>
+    <t>a,b \ c, d, e</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>a,b\c,d,e</t>
+  </si>
+  <si>
+    <t>формула для F</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>адрес b</t>
+  </si>
+  <si>
+    <t>инфо (a,c,d,e)</t>
+  </si>
 </sst>
 </file>
 
@@ -410,7 +431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,8 +522,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -759,11 +786,177 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -889,6 +1082,47 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1203,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A737F7B2-38C9-6A48-859E-BCB4386D6154}">
-  <dimension ref="A1:AX42"/>
+  <dimension ref="A1:BD42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1213,14 +1447,23 @@
     <col min="6" max="6" width="3" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
     <col min="24" max="24" width="5" customWidth="1"/>
-    <col min="25" max="25" width="4.33203125" customWidth="1"/>
-    <col min="26" max="26" width="3.5" customWidth="1"/>
-    <col min="27" max="27" width="4.1640625" customWidth="1"/>
-    <col min="28" max="28" width="3.5" customWidth="1"/>
+    <col min="25" max="25" width="3.5" customWidth="1"/>
+    <col min="26" max="26" width="4.1640625" customWidth="1"/>
+    <col min="27" max="27" width="3.5" customWidth="1"/>
+    <col min="28" max="28" width="4.33203125" customWidth="1"/>
     <col min="29" max="29" width="3.33203125" customWidth="1"/>
+    <col min="32" max="32" width="16.83203125" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
+    <col min="35" max="35" width="16.1640625" customWidth="1"/>
+    <col min="51" max="51" width="3.6640625" customWidth="1"/>
+    <col min="52" max="52" width="3.5" customWidth="1"/>
+    <col min="53" max="53" width="3.1640625" customWidth="1"/>
+    <col min="54" max="54" width="3.83203125" customWidth="1"/>
+    <col min="55" max="55" width="3.33203125" customWidth="1"/>
+    <col min="56" max="56" width="2.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23"/>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1245,9 +1488,8 @@
       <c r="V1" s="23"/>
       <c r="W1" s="23"/>
       <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A2" s="25"/>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -1267,7 +1509,7 @@
       <c r="Q2" s="26"/>
       <c r="R2" s="27"/>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +1543,7 @@
       <c r="Q3" s="29"/>
       <c r="R3" s="30"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="49">
         <v>0</v>
       </c>
@@ -1332,26 +1574,26 @@
       <c r="P4" s="29"/>
       <c r="Q4" s="29"/>
       <c r="R4" s="30"/>
-      <c r="X4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="1" t="s">
+      <c r="X4" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="AA4" s="62" t="s">
+      <c r="Z4" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AA4" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AB4" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="70" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A5" s="50">
         <v>0</v>
       </c>
@@ -1382,26 +1624,45 @@
       <c r="P5" s="29"/>
       <c r="Q5" s="29"/>
       <c r="R5" s="30"/>
-      <c r="X5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>0</v>
+      <c r="W5" s="91"/>
+      <c r="X5" s="86">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="87">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="87">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="87">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="73">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BB5" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50">
         <v>0</v>
       </c>
@@ -1432,26 +1693,45 @@
       <c r="P6" s="29"/>
       <c r="Q6" s="29"/>
       <c r="R6" s="30"/>
-      <c r="X6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="5">
-        <v>1</v>
+      <c r="W6" s="91"/>
+      <c r="X6" s="74">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="75">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="75">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="76">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="77">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="49">
         <v>0</v>
       </c>
@@ -1482,26 +1762,45 @@
       <c r="P7" s="29"/>
       <c r="Q7" s="29"/>
       <c r="R7" s="30"/>
-      <c r="X7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="5">
+      <c r="W7" s="91"/>
+      <c r="X7" s="74">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="75">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="75">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="75">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="80">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="4">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="50">
         <v>0</v>
       </c>
@@ -1532,26 +1831,45 @@
       <c r="P8" s="29"/>
       <c r="Q8" s="29"/>
       <c r="R8" s="30"/>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>0</v>
+      <c r="W8" s="91"/>
+      <c r="X8" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="89">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="89">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="89">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="76">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="81">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD8" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>0</v>
       </c>
@@ -1582,26 +1900,45 @@
       <c r="P9" s="29"/>
       <c r="Q9" s="29"/>
       <c r="R9" s="30"/>
-      <c r="X9" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="5">
-        <v>1</v>
+      <c r="W9" s="91"/>
+      <c r="X9" s="74">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="75">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="75">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="75">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="80">
+        <v>1</v>
+      </c>
+      <c r="AY9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC9" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD9" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>0</v>
       </c>
@@ -1632,26 +1969,45 @@
       <c r="P10" s="29"/>
       <c r="Q10" s="29"/>
       <c r="R10" s="30"/>
-      <c r="X10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>0</v>
+      <c r="W10" s="91"/>
+      <c r="X10" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="89">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="89">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="89">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="76">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="81">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="4">
+        <v>1</v>
+      </c>
+      <c r="BB10" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A11" s="50">
         <v>0</v>
       </c>
@@ -1682,26 +2038,45 @@
       <c r="P11" s="26"/>
       <c r="Q11" s="26"/>
       <c r="R11" s="27"/>
-      <c r="X11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="1">
+      <c r="W11" s="91"/>
+      <c r="X11" s="86">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="87">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="87">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="87">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="73">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB11" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="49">
         <v>0</v>
       </c>
@@ -1734,22 +2109,23 @@
       <c r="P12" s="29"/>
       <c r="Q12" s="29"/>
       <c r="R12" s="30"/>
-      <c r="X12" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="5">
+      <c r="W12" s="91"/>
+      <c r="X12" s="74">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="75">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="75">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="76">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="77">
         <v>1</v>
       </c>
       <c r="AF12" s="59" t="s">
@@ -1764,8 +2140,26 @@
       <c r="AR12" s="59"/>
       <c r="AS12" s="59"/>
       <c r="AT12" s="59"/>
+      <c r="AY12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC12" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="50">
         <v>0</v>
       </c>
@@ -1814,31 +2208,31 @@
         <v>100</v>
       </c>
       <c r="R13" s="30"/>
-      <c r="X13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE13" s="3" t="s">
+      <c r="X13" s="86">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="87">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="87">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="87">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="73">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE13" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="AF13" s="3" t="s">
+      <c r="AF13" s="65" t="s">
         <v>12</v>
       </c>
       <c r="AG13" s="3" t="s">
@@ -1860,7 +2254,7 @@
         <v>100</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AP13" s="3" t="s">
         <v>11</v>
@@ -1886,8 +2280,26 @@
       <c r="AW13" s="1">
         <v>100</v>
       </c>
+      <c r="AY13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="4">
+        <v>1</v>
+      </c>
+      <c r="BB13" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC13" s="4">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50">
         <v>0</v>
       </c>
@@ -1928,51 +2340,63 @@
       </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="30"/>
-      <c r="X14" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="3" t="s">
+      <c r="X14" s="74">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="75">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="75">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="76">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="77">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="AE14" s="45"/>
-      <c r="AF14" s="45" t="s">
+      <c r="AE14" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF14" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="AG14" s="45"/>
-      <c r="AH14" s="45" t="s">
+      <c r="AG14" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH14" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="AI14" s="45"/>
-      <c r="AJ14" s="45" t="s">
+      <c r="AI14" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ14" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="AK14" s="46">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="46"/>
+      <c r="AK14" s="66">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="67">
+        <v>1</v>
+      </c>
       <c r="AO14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AP14" s="45"/>
+      <c r="AP14" s="45" t="s">
+        <v>61</v>
+      </c>
       <c r="AQ14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="AR14" s="45"/>
+      <c r="AR14" s="45" t="s">
+        <v>61</v>
+      </c>
       <c r="AS14" s="45" t="s">
         <v>18</v>
       </c>
@@ -1984,8 +2408,26 @@
         <v>1</v>
       </c>
       <c r="AW14" s="46"/>
+      <c r="AY14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="58">
+        <v>1</v>
+      </c>
+      <c r="BA14" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB14" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="50">
         <v>0</v>
       </c>
@@ -2026,41 +2468,49 @@
         <v>1</v>
       </c>
       <c r="R15" s="30"/>
-      <c r="X15" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="3" t="s">
+      <c r="X15" s="78">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="79">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="79">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="80">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="45" t="s">
+      <c r="AE15" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="AF15" s="45"/>
-      <c r="AG15" s="45" t="s">
+      <c r="AF15" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="AH15" s="45"/>
-      <c r="AI15" s="45" t="s">
+      <c r="AG15" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="AJ15" s="45"/>
-      <c r="AK15" s="46"/>
-      <c r="AL15" s="46">
+      <c r="AH15" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI15" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ15" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK15" s="66">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="67">
         <v>1</v>
       </c>
       <c r="AO15" s="3" t="s">
@@ -2082,8 +2532,26 @@
       <c r="AW15" s="46">
         <v>1</v>
       </c>
+      <c r="AY15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="58">
+        <v>1</v>
+      </c>
+      <c r="BA15" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="4">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50">
         <v>0</v>
       </c>
@@ -2124,41 +2592,49 @@
         <v>1</v>
       </c>
       <c r="R16" s="30"/>
-      <c r="X16" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD16" s="3" t="s">
+      <c r="X16" s="74">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="75">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="75">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="76">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="77">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="AE16" s="45" t="s">
+      <c r="AE16" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF16" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="AF16" s="45"/>
-      <c r="AG16" s="45" t="s">
+      <c r="AG16" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH16" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="AH16" s="45"/>
-      <c r="AI16" s="45"/>
-      <c r="AJ16" s="45"/>
-      <c r="AK16" s="46">
-        <v>1</v>
-      </c>
-      <c r="AL16" s="46">
+      <c r="AI16" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ16" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK16" s="66">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="67">
         <v>1</v>
       </c>
       <c r="AO16" s="3" t="s">
@@ -2180,8 +2656,26 @@
       <c r="AW16" s="46">
         <v>1</v>
       </c>
+      <c r="AY16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="58">
+        <v>1</v>
+      </c>
+      <c r="BA16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC16" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD16" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="49">
         <v>0</v>
       </c>
@@ -2224,45 +2718,51 @@
       </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="30"/>
-      <c r="X17" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="3" t="s">
+      <c r="X17" s="78">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="79">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="79">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="80">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="AE17" s="45"/>
-      <c r="AF17" s="45" t="s">
+      <c r="AE17" s="66" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF17" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="AG17" s="45" t="s">
+      <c r="AG17" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="AH17" s="45" t="s">
+      <c r="AH17" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI17" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="AI17" s="45" t="s">
+      <c r="AJ17" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="AJ17" s="45"/>
-      <c r="AK17" s="46">
-        <v>1</v>
-      </c>
-      <c r="AL17" s="46"/>
+      <c r="AK17" s="66">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="67">
+        <v>1</v>
+      </c>
       <c r="AO17" s="3" t="s">
         <v>10</v>
       </c>
@@ -2284,8 +2784,26 @@
         <v>1</v>
       </c>
       <c r="AW17" s="46"/>
+      <c r="AY17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="58">
+        <v>1</v>
+      </c>
+      <c r="BA17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB17" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC17" s="4">
+        <v>1</v>
+      </c>
+      <c r="BD17" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:50" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>0</v>
       </c>
@@ -2316,26 +2834,44 @@
       <c r="P18" s="29"/>
       <c r="Q18" s="29"/>
       <c r="R18" s="30"/>
-      <c r="X18" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="1">
-        <v>0</v>
+      <c r="X18" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="89">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="89">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="89">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="76">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="81">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="58">
+        <v>1</v>
+      </c>
+      <c r="BA18" s="4">
+        <v>1</v>
+      </c>
+      <c r="BB18" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC18" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD18" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:56" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50">
         <v>0</v>
       </c>
@@ -2388,26 +2924,44 @@
       </c>
       <c r="S19" s="44"/>
       <c r="T19" s="29"/>
-      <c r="X19" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="1">
+      <c r="X19" s="86">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="87">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="87">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="87">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="73">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="58">
+        <v>1</v>
+      </c>
+      <c r="BA19" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB19" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC19" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:56" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>1</v>
       </c>
@@ -2438,25 +2992,25 @@
       <c r="P20" s="33"/>
       <c r="Q20" s="33"/>
       <c r="R20" s="36"/>
-      <c r="X20" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD20" s="34" t="s">
+      <c r="X20" s="74">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="75">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="75">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="76">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="77">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="21" t="s">
         <v>40</v>
       </c>
       <c r="AE20" s="20" t="s">
@@ -2516,8 +3070,26 @@
       <c r="AX20" s="35" t="s">
         <v>28</v>
       </c>
+      <c r="AY20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="58">
+        <v>1</v>
+      </c>
+      <c r="BA20" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB20" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC20" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD20" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:50" ht="18" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:56" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="50">
         <v>1</v>
       </c>
@@ -2569,26 +3141,44 @@
         <v>26</v>
       </c>
       <c r="S21" s="7"/>
-      <c r="X21" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="1">
-        <v>0</v>
+      <c r="X21" s="86">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="87">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="87">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="87">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="73">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="58">
+        <v>1</v>
+      </c>
+      <c r="BA21" s="4">
+        <v>1</v>
+      </c>
+      <c r="BB21" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC21" s="4">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="5">
+        <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="49">
         <v>1</v>
       </c>
@@ -2639,22 +3229,22 @@
       <c r="R22" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="X22" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="5">
+      <c r="X22" s="74">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="75">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="75">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="76">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="77">
         <v>1</v>
       </c>
       <c r="AD22" t="s">
@@ -2687,8 +3277,26 @@
       <c r="AS22" t="s">
         <v>57</v>
       </c>
+      <c r="AY22" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ22" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB22" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC22" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD22" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A23" s="50">
         <v>1</v>
       </c>
@@ -2721,25 +3329,25 @@
       <c r="P23" s="29"/>
       <c r="Q23" s="29"/>
       <c r="R23" s="30"/>
-      <c r="X23" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="54">
+      <c r="X23" s="86">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="87">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="87">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="87">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="73">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="85">
         <v>9</v>
       </c>
       <c r="AE23" s="56">
@@ -2769,8 +3377,26 @@
       <c r="AS23" s="54">
         <v>8</v>
       </c>
+      <c r="AY23" s="4">
+        <v>1</v>
+      </c>
+      <c r="AZ23" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA23" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="63">
+        <v>0</v>
+      </c>
+      <c r="BC23" s="4">
+        <v>1</v>
+      </c>
+      <c r="BD23" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="50">
         <v>1</v>
       </c>
@@ -2803,26 +3429,44 @@
       <c r="P24" s="29"/>
       <c r="Q24" s="29"/>
       <c r="R24" s="30"/>
-      <c r="X24" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="5">
-        <v>1</v>
+      <c r="X24" s="74">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="75">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="75">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="76">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="77">
+        <v>1</v>
+      </c>
+      <c r="AY24" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ24" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA24" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB24" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC24" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD24" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A25" s="49">
         <v>1</v>
       </c>
@@ -2853,26 +3497,44 @@
       <c r="P25" s="29"/>
       <c r="Q25" s="29"/>
       <c r="R25" s="30"/>
-      <c r="X25" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="5">
+      <c r="X25" s="78">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="79">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="79">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="80">
+        <v>1</v>
+      </c>
+      <c r="AY25" s="4">
+        <v>1</v>
+      </c>
+      <c r="AZ25" s="58">
+        <v>0</v>
+      </c>
+      <c r="BA25" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB25" s="63">
+        <v>1</v>
+      </c>
+      <c r="BC25" s="4">
+        <v>1</v>
+      </c>
+      <c r="BD25" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="50">
         <v>1</v>
       </c>
@@ -2903,30 +3565,53 @@
       <c r="P26" s="29"/>
       <c r="Q26" s="29"/>
       <c r="R26" s="30"/>
-      <c r="X26" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="64"/>
-      <c r="AG26" s="64"/>
-      <c r="AH26" s="64"/>
-      <c r="AI26" s="64"/>
+      <c r="X26" s="88">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="89">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="89">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="89">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="76">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="81">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG26" s="84" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH26" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT26" s="4">
+        <v>1</v>
+      </c>
+      <c r="AU26" s="58">
+        <v>0</v>
+      </c>
+      <c r="AV26" s="4">
+        <v>1</v>
+      </c>
+      <c r="AW26" s="63">
+        <v>0</v>
+      </c>
+      <c r="AX26" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY26" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A27" s="49">
         <v>1</v>
       </c>
@@ -2957,30 +3642,49 @@
       <c r="P27" s="29"/>
       <c r="Q27" s="29"/>
       <c r="R27" s="30"/>
-      <c r="X27" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="5">
-        <v>1</v>
-      </c>
-      <c r="AF27" s="64"/>
-      <c r="AG27" s="64"/>
-      <c r="AH27" s="64"/>
-      <c r="AI27" s="64"/>
+      <c r="X27" s="78">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="79">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="79">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="72">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="80">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG27" s="69"/>
+      <c r="AH27" s="68"/>
+      <c r="AT27" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU27" s="58">
+        <v>0</v>
+      </c>
+      <c r="AV27" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW27" s="63">
+        <v>0</v>
+      </c>
+      <c r="AX27" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY27" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>1</v>
       </c>
@@ -3011,30 +3715,47 @@
       <c r="P28" s="29"/>
       <c r="Q28" s="29"/>
       <c r="R28" s="30"/>
-      <c r="X28" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="58">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="64"/>
-      <c r="AG28" s="64"/>
-      <c r="AH28" s="64"/>
-      <c r="AI28" s="64"/>
+      <c r="X28" s="88">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="89">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="89">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="89">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="76">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="81">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="69"/>
+      <c r="AG28" s="68"/>
+      <c r="AH28" s="68"/>
+      <c r="AT28" s="4">
+        <v>1</v>
+      </c>
+      <c r="AU28" s="58">
+        <v>0</v>
+      </c>
+      <c r="AV28" s="4">
+        <v>1</v>
+      </c>
+      <c r="AW28" s="63">
+        <v>1</v>
+      </c>
+      <c r="AX28" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY28" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A29" s="50">
         <v>1</v>
       </c>
@@ -3065,30 +3786,47 @@
       <c r="P29" s="29"/>
       <c r="Q29" s="29"/>
       <c r="R29" s="30"/>
-      <c r="X29" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="64"/>
-      <c r="AG29" s="64"/>
-      <c r="AH29" s="64"/>
-      <c r="AI29" s="64"/>
+      <c r="X29" s="86">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="87">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="87">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="87">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="73">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="69"/>
+      <c r="AG29" s="68"/>
+      <c r="AH29" s="68"/>
+      <c r="AT29" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU29" s="58">
+        <v>0</v>
+      </c>
+      <c r="AV29" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW29" s="63">
+        <v>1</v>
+      </c>
+      <c r="AX29" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY29" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="50">
         <v>1</v>
       </c>
@@ -3123,30 +3861,47 @@
       <c r="P30" s="29"/>
       <c r="Q30" s="29"/>
       <c r="R30" s="30"/>
-      <c r="X30" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="5">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="64"/>
-      <c r="AG30" s="64"/>
-      <c r="AH30" s="64"/>
-      <c r="AI30" s="64"/>
+      <c r="X30" s="74">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="75">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="75">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="76">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="77">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="69"/>
+      <c r="AG30" s="68"/>
+      <c r="AH30" s="68"/>
+      <c r="AT30" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU30" s="58">
+        <v>1</v>
+      </c>
+      <c r="AV30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW30" s="63">
+        <v>0</v>
+      </c>
+      <c r="AX30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY30" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A31" s="49">
         <v>1</v>
       </c>
@@ -3181,30 +3936,47 @@
       <c r="P31" s="29"/>
       <c r="Q31" s="29"/>
       <c r="R31" s="30"/>
-      <c r="X31" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y31" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC31" s="5">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="64"/>
-      <c r="AG31" s="64"/>
-      <c r="AH31" s="64"/>
-      <c r="AI31" s="64"/>
+      <c r="X31" s="78">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="79">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="79">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="80">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="69"/>
+      <c r="AG31" s="68"/>
+      <c r="AH31" s="68"/>
+      <c r="AT31" s="4">
+        <v>1</v>
+      </c>
+      <c r="AU31" s="58">
+        <v>1</v>
+      </c>
+      <c r="AV31" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW31" s="63">
+        <v>0</v>
+      </c>
+      <c r="AX31" s="4">
+        <v>1</v>
+      </c>
+      <c r="AY31" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="50">
         <v>1</v>
       </c>
@@ -3239,30 +4011,47 @@
       <c r="P32" s="29"/>
       <c r="Q32" s="29"/>
       <c r="R32" s="30"/>
-      <c r="X32" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="64"/>
-      <c r="AG32" s="64"/>
-      <c r="AH32" s="64"/>
-      <c r="AI32" s="64"/>
+      <c r="X32" s="88">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="89">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="89">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="89">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="76">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="81">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="69"/>
+      <c r="AG32" s="68"/>
+      <c r="AH32" s="68"/>
+      <c r="AT32" s="4">
+        <v>1</v>
+      </c>
+      <c r="AU32" s="58">
+        <v>1</v>
+      </c>
+      <c r="AV32" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW32" s="63">
+        <v>1</v>
+      </c>
+      <c r="AX32" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY32" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A33" s="50">
         <v>1</v>
       </c>
@@ -3297,30 +4086,47 @@
       <c r="P33" s="29"/>
       <c r="Q33" s="29"/>
       <c r="R33" s="30"/>
-      <c r="X33" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y33" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="5">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="64"/>
-      <c r="AG33" s="64"/>
-      <c r="AH33" s="64"/>
-      <c r="AI33" s="64"/>
+      <c r="X33" s="78">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="79">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="79">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="80">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="69"/>
+      <c r="AG33" s="68"/>
+      <c r="AH33" s="68"/>
+      <c r="AT33" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU33" s="58">
+        <v>1</v>
+      </c>
+      <c r="AV33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW33" s="63">
+        <v>1</v>
+      </c>
+      <c r="AX33" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY33" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:51" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="49">
         <v>1</v>
       </c>
@@ -3351,30 +4157,47 @@
       <c r="P34" s="29"/>
       <c r="Q34" s="29"/>
       <c r="R34" s="30"/>
-      <c r="X34" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="63">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="5">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="64"/>
-      <c r="AG34" s="64"/>
-      <c r="AH34" s="64"/>
-      <c r="AI34" s="64"/>
+      <c r="X34" s="74">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="75">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="75">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="75">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="76">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="77">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="69"/>
+      <c r="AG34" s="68"/>
+      <c r="AH34" s="68"/>
+      <c r="AT34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AU34" s="58">
+        <v>1</v>
+      </c>
+      <c r="AV34" s="4">
+        <v>1</v>
+      </c>
+      <c r="AW34" s="63">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:51" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51">
         <v>1</v>
       </c>
@@ -3405,92 +4228,138 @@
       <c r="P35" s="42"/>
       <c r="Q35" s="42"/>
       <c r="R35" s="43"/>
-      <c r="X35" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="64"/>
-      <c r="AG35" s="64"/>
-      <c r="AH35" s="64"/>
-      <c r="AI35" s="64"/>
+      <c r="X35" s="86">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="87">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="87">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="87">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="73">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="69"/>
+      <c r="AG35" s="68"/>
+      <c r="AH35" s="68"/>
+      <c r="AT35" s="4">
+        <v>1</v>
+      </c>
+      <c r="AU35" s="58">
+        <v>1</v>
+      </c>
+      <c r="AV35" s="4">
+        <v>1</v>
+      </c>
+      <c r="AW35" s="63">
+        <v>0</v>
+      </c>
+      <c r="AX35" s="4">
+        <v>1</v>
+      </c>
+      <c r="AY35" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="X36" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y36" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA36" s="63">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AC36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="64"/>
-      <c r="AG36" s="64"/>
-      <c r="AH36" s="64"/>
-      <c r="AI36" s="64"/>
+    <row r="36" spans="1:51" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="X36" s="88">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="89">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="89">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="89">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="76">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="81">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="69"/>
+      <c r="AG36" s="68"/>
+      <c r="AH36" s="68"/>
+      <c r="AT36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU36" s="58">
+        <v>1</v>
+      </c>
+      <c r="AV36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW36" s="63">
+        <v>1</v>
+      </c>
+      <c r="AX36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY36" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="AF37" s="64"/>
-      <c r="AG37" s="64"/>
-      <c r="AH37" s="64"/>
-      <c r="AI37" s="64"/>
+    <row r="37" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AF37" s="69"/>
+      <c r="AG37" s="68"/>
+      <c r="AH37" s="68"/>
+      <c r="AT37" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU37" s="58">
+        <v>1</v>
+      </c>
+      <c r="AV37" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW37" s="63">
+        <v>1</v>
+      </c>
+      <c r="AX37" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY37" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="AF38" s="64"/>
-      <c r="AG38" s="64"/>
-      <c r="AH38" s="64"/>
-      <c r="AI38" s="64"/>
+    <row r="38" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AF38" s="69"/>
+      <c r="AG38" s="68"/>
+      <c r="AH38" s="68"/>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="AF39" s="64"/>
-      <c r="AG39" s="64"/>
-      <c r="AH39" s="64"/>
-      <c r="AI39" s="64"/>
+    <row r="39" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AF39" s="69"/>
+      <c r="AG39" s="68"/>
+      <c r="AH39" s="68"/>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="AF40" s="64"/>
-      <c r="AG40" s="64"/>
-      <c r="AH40" s="64"/>
-      <c r="AI40" s="64"/>
+    <row r="40" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AF40" s="69"/>
+      <c r="AG40" s="68"/>
+      <c r="AH40" s="68"/>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="AF41" s="64"/>
-      <c r="AG41" s="64"/>
-      <c r="AH41" s="64"/>
-      <c r="AI41" s="64"/>
+    <row r="41" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AF41" s="69"/>
+      <c r="AG41" s="68"/>
+      <c r="AH41" s="68"/>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="AF42" s="64"/>
-      <c r="AG42" s="64"/>
-      <c r="AH42" s="64"/>
-      <c r="AI42" s="64"/>
+    <row r="42" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="AF42" s="69"/>
+      <c r="AG42" s="68"/>
+      <c r="AH42" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A1:X1"/>
     <mergeCell ref="H3:N10"/>
     <mergeCell ref="K12:O12"/>
     <mergeCell ref="AQ12:AT12"/>

--- a/labs/4.lab/4.lab.xlsx
+++ b/labs/4.lab/4.lab.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rod/Documents/ehu/dt/labs/4.lab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EFC2E4-C239-F84F-BAE6-AF1ED79007AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B746B8-A40A-3E46-A2AE-A15A95B00E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{B4FD20D9-57F3-4747-AA10-0A42781B4A42}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="21440" windowHeight="22400" xr2:uid="{B4FD20D9-57F3-4747-AA10-0A42781B4A42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="126">
   <si>
     <t>a</t>
   </si>
@@ -365,12 +365,6 @@
     <t xml:space="preserve">e ~e </t>
   </si>
   <si>
-    <t>для мультиплексора 8/1</t>
-  </si>
-  <si>
-    <t>для мультиплексора 16/1</t>
-  </si>
-  <si>
     <t>a,b \ c, d, e</t>
   </si>
   <si>
@@ -386,17 +380,221 @@
     <t>0000</t>
   </si>
   <si>
-    <t>адрес b</t>
-  </si>
-  <si>
-    <t>инфо (a,c,d,e)</t>
+    <t>CONST (a,c,d)</t>
+  </si>
+  <si>
+    <t>00 -&gt; 0
+10 -&gt; 1
+01 -&gt; 0
+11 -&gt; 1</t>
+  </si>
+  <si>
+    <t>F(e,b)</t>
+  </si>
+  <si>
+    <t>00 -&gt; 1
+10 -&gt; 0
+01 -&gt; 1
+11 -&gt; 1</t>
+  </si>
+  <si>
+    <t>000  →  [0,1,0,1]  →  I0 = e</t>
+  </si>
+  <si>
+    <t>001  →  [1,0,1,1]  →  I1 = b OR ~e</t>
+  </si>
+  <si>
+    <t>010  →  [1,0,1,0]  →  I2 = ~e</t>
+  </si>
+  <si>
+    <t>011  →  [0,1,0,1]  →  I3 = e</t>
+  </si>
+  <si>
+    <t>100  →  [0,1,0,1]  →  I4 = e</t>
+  </si>
+  <si>
+    <t>101  →  [0,1,1,0]  →  I5 = b XOR e</t>
+  </si>
+  <si>
+    <t>110  →  [1,0,1,1]  →  I6 = b OR ~e</t>
+  </si>
+  <si>
+    <t>111  →  [1,0,0,0]  →  I7 = ~b AND ~e</t>
+  </si>
+  <si>
+    <t>00 -&gt; 1
+10 -&gt; 0
+01 -&gt; 1
+11 -&gt; 0</t>
+  </si>
+  <si>
+    <t>b OR ~e</t>
+  </si>
+  <si>
+    <t>~e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">011 </t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>00 -&gt; 0
+10 -&gt; 1
+01 -&gt; 1
+11 -&gt; 0</t>
+  </si>
+  <si>
+    <t>b XOR e</t>
+  </si>
+  <si>
+    <t>00 -&gt; 1
+10 -&gt; 0
+01 -&gt; 0
+11 -&gt; 0</t>
+  </si>
+  <si>
+    <t>~b AND ~e</t>
+  </si>
+  <si>
+    <t>CONST (a,c,d,e)</t>
+  </si>
+  <si>
+    <t>для мультиплексора 16:1</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>0 -&gt; 0
+1 -&gt; 0</t>
+  </si>
+  <si>
+    <t>0001</t>
+  </si>
+  <si>
+    <t>0 -&gt; 1
+1 -&gt; 1</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>0011</t>
+  </si>
+  <si>
+    <t>0 -&gt; 0
+1 -&gt; 1</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>0111</t>
+  </si>
+  <si>
+    <t>0 -&gt; 1
+1 -&gt;1</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>0 -&gt;1 
+1 -&gt; 1</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>0 -&gt; 1
+1 -&gt; 0</t>
+  </si>
+  <si>
+    <t>~b</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>I0</t>
+  </si>
+  <si>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>I3</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>I5</t>
+  </si>
+  <si>
+    <t>I6</t>
+  </si>
+  <si>
+    <t>I7</t>
+  </si>
+  <si>
+    <t>I8</t>
+  </si>
+  <si>
+    <t>I9</t>
+  </si>
+  <si>
+    <t>I10</t>
+  </si>
+  <si>
+    <t>I11</t>
+  </si>
+  <si>
+    <t>I12</t>
+  </si>
+  <si>
+    <t>I13</t>
+  </si>
+  <si>
+    <t>I14</t>
+  </si>
+  <si>
+    <t>I15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -430,8 +628,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -528,6 +755,78 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -787,19 +1086,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -866,36 +1152,6 @@
       </right>
       <top style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
       </top>
       <bottom style="medium">
         <color theme="1"/>
@@ -952,11 +1208,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1008,17 +1309,10 @@
     <xf numFmtId="49" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1026,7 +1320,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1041,9 +1335,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1053,76 +1344,162 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1437,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A737F7B2-38C9-6A48-859E-BCB4386D6154}">
-  <dimension ref="A1:BD42"/>
+  <dimension ref="A1:BD46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1455,62 +1832,63 @@
     <col min="32" max="32" width="16.83203125" customWidth="1"/>
     <col min="34" max="34" width="16" customWidth="1"/>
     <col min="35" max="35" width="16.1640625" customWidth="1"/>
+    <col min="45" max="45" width="13.5" customWidth="1"/>
     <col min="51" max="51" width="3.6640625" customWidth="1"/>
-    <col min="52" max="52" width="3.5" customWidth="1"/>
-    <col min="53" max="53" width="3.1640625" customWidth="1"/>
-    <col min="54" max="54" width="3.83203125" customWidth="1"/>
-    <col min="55" max="55" width="3.33203125" customWidth="1"/>
+    <col min="52" max="52" width="3.1640625" customWidth="1"/>
+    <col min="53" max="53" width="3.83203125" customWidth="1"/>
+    <col min="54" max="54" width="3.33203125" customWidth="1"/>
+    <col min="55" max="55" width="3.5" customWidth="1"/>
     <col min="56" max="56" width="2.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
+      <c r="A1" s="68"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68"/>
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
     </row>
     <row r="2" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="27"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="25"/>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1528,23 +1906,19 @@
       <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="48" t="s">
+      <c r="H3" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="30"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="R3" s="27"/>
     </row>
     <row r="4" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="49">
+      <c r="A4" s="44">
         <v>0</v>
       </c>
       <c r="B4" s="2">
@@ -1562,39 +1936,35 @@
       <c r="F4" s="1">
         <v>0</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="30"/>
-      <c r="X4" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="70" t="s">
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="R4" s="27"/>
+      <c r="X4" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="Z4" s="90" t="s">
+      <c r="Z4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="AA4" s="70" t="s">
+      <c r="AA4" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="AB4" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="70" t="s">
+      <c r="AB4" s="66" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="60" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A5" s="50">
+      <c r="A5" s="45">
         <v>0</v>
       </c>
       <c r="B5" s="4">
@@ -1612,58 +1982,54 @@
       <c r="F5" s="5">
         <v>1</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="30"/>
-      <c r="W5" s="91"/>
-      <c r="X5" s="86">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="87">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="87">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="73">
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="R5" s="27"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="78">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="79">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="79">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="78">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="80">
         <v>0</v>
       </c>
       <c r="AY5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AZ5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA5" s="1" t="s">
+      <c r="AZ5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="BB5" s="62" t="s">
+      <c r="BA5" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="BC5" s="1" t="s">
+      <c r="BB5" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="BC5" s="52" t="s">
+        <v>1</v>
       </c>
       <c r="BD5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="50">
+      <c r="A6" s="45">
         <v>0</v>
       </c>
       <c r="B6" s="4">
@@ -1681,58 +2047,54 @@
       <c r="F6" s="5">
         <v>1</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="30"/>
-      <c r="W6" s="91"/>
-      <c r="X6" s="74">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="75">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="75">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="76">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="77">
-        <v>1</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA6" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB6" s="63">
-        <v>0</v>
-      </c>
-      <c r="BC6" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD6" s="1">
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="R6" s="27"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="81">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="82">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="82">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="82">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="81">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="83">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="131">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="131">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="131">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="131">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="131">
+        <v>0</v>
+      </c>
+      <c r="BD6" s="132">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49">
+      <c r="A7" s="44">
         <v>0</v>
       </c>
       <c r="B7" s="2">
@@ -1750,58 +2112,54 @@
       <c r="F7" s="1">
         <v>0</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="30"/>
-      <c r="W7" s="91"/>
-      <c r="X7" s="74">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="75">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="75">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="75">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="80">
-        <v>1</v>
-      </c>
-      <c r="AY7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA7" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB7" s="63">
-        <v>0</v>
-      </c>
-      <c r="BC7" s="4">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="5">
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="69"/>
+      <c r="R7" s="27"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="86">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="62">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="62">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="86">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="87">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="137">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="137">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="137">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="137">
+        <v>1</v>
+      </c>
+      <c r="BC7" s="137">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="138">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="50">
+      <c r="A8" s="45">
         <v>0</v>
       </c>
       <c r="B8" s="4">
@@ -1819,58 +2177,54 @@
       <c r="F8" s="5">
         <v>1</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="30"/>
-      <c r="W8" s="91"/>
-      <c r="X8" s="88">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="89">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="89">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="89">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="76">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="81">
-        <v>0</v>
-      </c>
-      <c r="AY8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ8" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA8" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB8" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC8" s="4">
-        <v>0</v>
-      </c>
-      <c r="BD8" s="5">
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="R8" s="27"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="86">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="62">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="62">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="86">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="88">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="53">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="53">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="53">
+        <v>1</v>
+      </c>
+      <c r="BB8" s="53">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="53">
+        <v>0</v>
+      </c>
+      <c r="BD8" s="52">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="49">
+      <c r="A9" s="44">
         <v>0</v>
       </c>
       <c r="B9" s="2">
@@ -1888,58 +2242,54 @@
       <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="30"/>
-      <c r="W9" s="91"/>
-      <c r="X9" s="74">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="75">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="75">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="75">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="80">
-        <v>1</v>
-      </c>
-      <c r="AY9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA9" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB9" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC9" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD9" s="1">
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="69"/>
+      <c r="N9" s="69"/>
+      <c r="R9" s="27"/>
+      <c r="W9" s="67"/>
+      <c r="X9" s="92">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="93">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="93">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="93">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="92">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="94">
+        <v>1</v>
+      </c>
+      <c r="AY9" s="139">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="139">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="139">
+        <v>1</v>
+      </c>
+      <c r="BB9" s="139">
+        <v>1</v>
+      </c>
+      <c r="BC9" s="139">
+        <v>0</v>
+      </c>
+      <c r="BD9" s="140">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49">
+      <c r="A10" s="44">
         <v>0</v>
       </c>
       <c r="B10" s="2">
@@ -1957,47 +2307,43 @@
       <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="30"/>
-      <c r="W10" s="91"/>
-      <c r="X10" s="88">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="89">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="89">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="89">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="76">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="81">
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="69"/>
+      <c r="R10" s="27"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="92">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="93">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="93">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="93">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="92">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="95">
         <v>0</v>
       </c>
       <c r="AY10" s="4">
         <v>0</v>
       </c>
-      <c r="AZ10" s="58">
-        <v>0</v>
+      <c r="AZ10" s="4">
+        <v>1</v>
       </c>
       <c r="BA10" s="4">
-        <v>1</v>
-      </c>
-      <c r="BB10" s="63">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="4">
         <v>0</v>
       </c>
       <c r="BC10" s="4">
@@ -2008,7 +2354,7 @@
       </c>
     </row>
     <row r="11" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A11" s="50">
+      <c r="A11" s="45">
         <v>0</v>
       </c>
       <c r="B11" s="4">
@@ -2026,58 +2372,56 @@
       <c r="F11" s="5">
         <v>1</v>
       </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="27"/>
-      <c r="W11" s="91"/>
-      <c r="X11" s="86">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="87">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="87">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="73">
-        <v>0</v>
-      </c>
-      <c r="AY11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB11" s="63">
-        <v>0</v>
-      </c>
-      <c r="BC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD11" s="1">
+      <c r="I11" s="23"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="25"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="98">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="99">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="99">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="99">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="98">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="100">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="57">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="57">
+        <v>1</v>
+      </c>
+      <c r="BA11" s="57">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="57">
+        <v>1</v>
+      </c>
+      <c r="BC11" s="57">
+        <v>0</v>
+      </c>
+      <c r="BD11" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="49">
+      <c r="A12" s="44">
         <v>0</v>
       </c>
       <c r="B12" s="2">
@@ -2095,72 +2439,65 @@
       <c r="F12" s="1">
         <v>0</v>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="24" t="s">
+      <c r="I12" s="26"/>
+      <c r="K12" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="30"/>
-      <c r="W12" s="91"/>
-      <c r="X12" s="74">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="75">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="75">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="76">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="77">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="59" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG12" s="59"/>
-      <c r="AH12" s="59"/>
-      <c r="AI12" s="59"/>
-      <c r="AQ12" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="AR12" s="59"/>
-      <c r="AS12" s="59"/>
-      <c r="AT12" s="59"/>
-      <c r="AY12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB12" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC12" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD12" s="1">
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="R12" s="27"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="101">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="102">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="102">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="102">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="101">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="103">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="74"/>
+      <c r="AG12" s="74"/>
+      <c r="AH12" s="74"/>
+      <c r="AI12" s="71"/>
+      <c r="AQ12" s="71" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR12" s="71"/>
+      <c r="AS12" s="71"/>
+      <c r="AT12" s="71"/>
+      <c r="AY12" s="141">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="141">
+        <v>1</v>
+      </c>
+      <c r="BA12" s="141">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="141">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="141">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="142">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="50">
+      <c r="A13" s="45">
         <v>0</v>
       </c>
       <c r="B13" s="4">
@@ -2178,9 +2515,7 @@
       <c r="F13" s="5">
         <v>1</v>
       </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="31" t="s">
+      <c r="I13" s="28" t="s">
         <v>15</v>
       </c>
       <c r="J13" s="3" t="s">
@@ -2207,54 +2542,54 @@
       <c r="Q13" s="1">
         <v>100</v>
       </c>
-      <c r="R13" s="30"/>
-      <c r="X13" s="86">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="87">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="87">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="72">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="73">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="82" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE13" s="65" t="s">
+      <c r="R13" s="27"/>
+      <c r="X13" s="78">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="79">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="79">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="78">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="80">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE13" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="AF13" s="65" t="s">
+      <c r="AF13" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="AG13" s="3" t="s">
+      <c r="AG13" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="AH13" s="3" t="s">
+      <c r="AH13" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="AI13" s="3" t="s">
+      <c r="AI13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="AJ13" s="3" t="s">
+      <c r="AJ13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="AK13" s="1">
+      <c r="AK13" s="60">
         <v>101</v>
       </c>
-      <c r="AL13" s="1">
+      <c r="AL13" s="60">
         <v>100</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AP13" s="3" t="s">
         <v>11</v>
@@ -2280,27 +2615,27 @@
       <c r="AW13" s="1">
         <v>100</v>
       </c>
-      <c r="AY13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA13" s="4">
-        <v>1</v>
-      </c>
-      <c r="BB13" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC13" s="4">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="5">
+      <c r="AY13" s="143">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="143">
+        <v>1</v>
+      </c>
+      <c r="BA13" s="143">
+        <v>1</v>
+      </c>
+      <c r="BB13" s="143">
+        <v>1</v>
+      </c>
+      <c r="BC13" s="143">
+        <v>0</v>
+      </c>
+      <c r="BD13" s="144">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50">
+      <c r="A14" s="45">
         <v>0</v>
       </c>
       <c r="B14" s="4">
@@ -2318,9 +2653,7 @@
       <c r="F14" s="5">
         <v>1</v>
       </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J14" s="3"/>
@@ -2339,96 +2672,96 @@
         <v>1</v>
       </c>
       <c r="Q14" s="1"/>
-      <c r="R14" s="30"/>
-      <c r="X14" s="74">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="75">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="75">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="76">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="77">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="83" t="s">
+      <c r="R14" s="27"/>
+      <c r="X14" s="81">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="82">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="82">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="82">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="81">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="83">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="AE14" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF14" s="67" t="s">
+      <c r="AE14" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF14" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AG14" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH14" s="67" t="s">
+      <c r="AG14" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH14" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="AI14" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ14" s="67" t="s">
+      <c r="AI14" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ14" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AK14" s="66">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="67">
+      <c r="AK14" s="76">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="77">
         <v>1</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AP14" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="AQ14" s="45" t="s">
+      <c r="AP14" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="AQ14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AR14" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="AS14" s="45" t="s">
+      <c r="AR14" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="AS14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AT14" s="45"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AT14" s="41"/>
+      <c r="AU14" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AV14" s="46">
-        <v>1</v>
-      </c>
-      <c r="AW14" s="46"/>
-      <c r="AY14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ14" s="58">
-        <v>1</v>
-      </c>
-      <c r="BA14" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB14" s="63">
-        <v>0</v>
-      </c>
-      <c r="BC14" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD14" s="1">
+      <c r="AV14" s="42">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="42"/>
+      <c r="AY14" s="131">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="131">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="131">
+        <v>0</v>
+      </c>
+      <c r="BB14" s="131">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="131">
+        <v>1</v>
+      </c>
+      <c r="BD14" s="132">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50">
+      <c r="A15" s="45">
         <v>0</v>
       </c>
       <c r="B15" s="4">
@@ -2446,9 +2779,7 @@
       <c r="F15" s="5">
         <v>1</v>
       </c>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="31" t="s">
+      <c r="I15" s="28" t="s">
         <v>8</v>
       </c>
       <c r="J15" s="9" t="s">
@@ -2467,92 +2798,92 @@
       <c r="Q15" s="18">
         <v>1</v>
       </c>
-      <c r="R15" s="30"/>
-      <c r="X15" s="78">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="79">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="79">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="79">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="72">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="80">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="83" t="s">
+      <c r="R15" s="27"/>
+      <c r="X15" s="89">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="61">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="61">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="89">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="87">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="66" t="s">
+      <c r="AE15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="AF15" s="67" t="s">
+      <c r="AF15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AG15" s="66" t="s">
+      <c r="AG15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AH15" s="67" t="s">
+      <c r="AH15" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="AI15" s="66" t="s">
+      <c r="AI15" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="AJ15" s="67" t="s">
+      <c r="AJ15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AK15" s="66">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="67">
+      <c r="AK15" s="76">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="77">
         <v>1</v>
       </c>
       <c r="AO15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP15" s="45" t="s">
+      <c r="AP15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AQ15" s="45"/>
-      <c r="AR15" s="45" t="s">
+      <c r="AQ15" s="41"/>
+      <c r="AR15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AS15" s="45"/>
-      <c r="AT15" s="45" t="s">
+      <c r="AS15" s="41"/>
+      <c r="AT15" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AU15" s="45"/>
-      <c r="AV15" s="46"/>
-      <c r="AW15" s="46">
-        <v>1</v>
-      </c>
-      <c r="AY15" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ15" s="58">
-        <v>1</v>
-      </c>
-      <c r="BA15" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB15" s="63">
-        <v>0</v>
-      </c>
-      <c r="BC15" s="4">
-        <v>1</v>
-      </c>
-      <c r="BD15" s="5">
+      <c r="AU15" s="41"/>
+      <c r="AV15" s="42"/>
+      <c r="AW15" s="42">
+        <v>1</v>
+      </c>
+      <c r="AY15" s="137">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="137">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="137">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="137">
+        <v>1</v>
+      </c>
+      <c r="BC15" s="137">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="138">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50">
+      <c r="A16" s="45">
         <v>0</v>
       </c>
       <c r="B16" s="4">
@@ -2570,9 +2901,7 @@
       <c r="F16" s="5">
         <v>1</v>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="31" t="s">
+      <c r="I16" s="28" t="s">
         <v>9</v>
       </c>
       <c r="J16" s="9" t="s">
@@ -2591,92 +2920,92 @@
       <c r="Q16" s="12">
         <v>1</v>
       </c>
-      <c r="R16" s="30"/>
-      <c r="X16" s="74">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="75">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="75">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="76">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="77">
-        <v>1</v>
-      </c>
-      <c r="AD16" s="83" t="s">
+      <c r="R16" s="27"/>
+      <c r="X16" s="86">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="62">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="62">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="86">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="88">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="AE16" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF16" s="67" t="s">
+      <c r="AE16" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF16" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AG16" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH16" s="67" t="s">
+      <c r="AG16" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH16" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="AI16" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ16" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK16" s="66">
-        <v>1</v>
-      </c>
-      <c r="AL16" s="67">
+      <c r="AI16" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ16" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK16" s="76">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="77">
         <v>1</v>
       </c>
       <c r="AO16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AP16" s="45" t="s">
+      <c r="AP16" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AQ16" s="45"/>
-      <c r="AR16" s="45" t="s">
+      <c r="AQ16" s="41"/>
+      <c r="AR16" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AS16" s="45"/>
-      <c r="AT16" s="45"/>
-      <c r="AU16" s="45"/>
-      <c r="AV16" s="46">
-        <v>1</v>
-      </c>
-      <c r="AW16" s="46">
-        <v>1</v>
-      </c>
-      <c r="AY16" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="58">
-        <v>1</v>
-      </c>
-      <c r="BA16" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB16" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC16" s="4">
-        <v>0</v>
-      </c>
-      <c r="BD16" s="5">
+      <c r="AS16" s="41"/>
+      <c r="AT16" s="41"/>
+      <c r="AU16" s="41"/>
+      <c r="AV16" s="42">
+        <v>1</v>
+      </c>
+      <c r="AW16" s="42">
+        <v>1</v>
+      </c>
+      <c r="AY16" s="53">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="53">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="53">
+        <v>1</v>
+      </c>
+      <c r="BB16" s="53">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="53">
+        <v>1</v>
+      </c>
+      <c r="BD16" s="52">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="49">
+      <c r="A17" s="44">
         <v>0</v>
       </c>
       <c r="B17" s="2">
@@ -2694,9 +3023,7 @@
       <c r="F17" s="1">
         <v>0</v>
       </c>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="31" t="s">
+      <c r="I17" s="28" t="s">
         <v>10</v>
       </c>
       <c r="J17" s="3"/>
@@ -2717,94 +3044,94 @@
         <v>1</v>
       </c>
       <c r="Q17" s="1"/>
-      <c r="R17" s="30"/>
-      <c r="X17" s="78">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="79">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="79">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="79">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="72">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="80">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="83" t="s">
+      <c r="R17" s="27"/>
+      <c r="X17" s="96">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="97">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="97">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="97">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="96">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="94">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="AE17" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF17" s="67" t="s">
+      <c r="AE17" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF17" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AG17" s="66" t="s">
+      <c r="AG17" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AH17" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI17" s="66" t="s">
+      <c r="AH17" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI17" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="AJ17" s="67" t="s">
+      <c r="AJ17" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="AK17" s="66">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="67">
+      <c r="AK17" s="76">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="77">
         <v>1</v>
       </c>
       <c r="AO17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AP17" s="45"/>
-      <c r="AQ17" s="45" t="s">
+      <c r="AP17" s="41"/>
+      <c r="AQ17" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AR17" s="45" t="s">
+      <c r="AR17" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AS17" s="45" t="s">
+      <c r="AS17" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AT17" s="45" t="s">
+      <c r="AT17" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="AU17" s="45"/>
-      <c r="AV17" s="46">
-        <v>1</v>
-      </c>
-      <c r="AW17" s="46"/>
-      <c r="AY17" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="58">
-        <v>1</v>
-      </c>
-      <c r="BA17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB17" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC17" s="4">
-        <v>1</v>
-      </c>
-      <c r="BD17" s="5">
+      <c r="AU17" s="41"/>
+      <c r="AV17" s="42">
+        <v>1</v>
+      </c>
+      <c r="AW17" s="42"/>
+      <c r="AY17" s="139">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="139">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="139">
+        <v>1</v>
+      </c>
+      <c r="BB17" s="139">
+        <v>1</v>
+      </c>
+      <c r="BC17" s="139">
+        <v>1</v>
+      </c>
+      <c r="BD17" s="140">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49">
+      <c r="A18" s="44">
         <v>0</v>
       </c>
       <c r="B18" s="2">
@@ -2822,57 +3149,53 @@
       <c r="F18" s="1">
         <v>0</v>
       </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="30"/>
-      <c r="X18" s="88">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="89">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="89">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="89">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="76">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="81">
+      <c r="I18" s="29"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="R18" s="27"/>
+      <c r="X18" s="92">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="93">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="93">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="93">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="92">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="95">
         <v>0</v>
       </c>
       <c r="AY18" s="4">
         <v>0</v>
       </c>
-      <c r="AZ18" s="58">
+      <c r="AZ18" s="4">
         <v>1</v>
       </c>
       <c r="BA18" s="4">
-        <v>1</v>
-      </c>
-      <c r="BB18" s="63">
+        <v>0</v>
+      </c>
+      <c r="BB18" s="4">
         <v>0</v>
       </c>
       <c r="BC18" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD18" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:56" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50">
+      <c r="A19" s="45">
         <v>0</v>
       </c>
       <c r="B19" s="4">
@@ -2890,9 +3213,7 @@
       <c r="F19" s="5">
         <v>1</v>
       </c>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="34" t="s">
+      <c r="I19" s="31" t="s">
         <v>40</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -2919,50 +3240,49 @@
       <c r="Q19" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="R19" s="35" t="s">
+      <c r="R19" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="S19" s="44"/>
-      <c r="T19" s="29"/>
-      <c r="X19" s="86">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="87">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="87">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="72">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="73">
-        <v>0</v>
-      </c>
-      <c r="AY19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ19" s="58">
-        <v>1</v>
-      </c>
-      <c r="BA19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB19" s="63">
-        <v>0</v>
-      </c>
-      <c r="BC19" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD19" s="1">
+      <c r="S19" s="40"/>
+      <c r="X19" s="98">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="99">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="99">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="99">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="98">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="100">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="57">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="57">
+        <v>1</v>
+      </c>
+      <c r="BA19" s="57">
+        <v>0</v>
+      </c>
+      <c r="BB19" s="57">
+        <v>1</v>
+      </c>
+      <c r="BC19" s="57">
+        <v>1</v>
+      </c>
+      <c r="BD19" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:56" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="49">
+      <c r="A20" s="44">
         <v>1</v>
       </c>
       <c r="B20" s="2">
@@ -2980,34 +3300,32 @@
       <c r="F20" s="1">
         <v>0</v>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="36"/>
-      <c r="X20" s="74">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="75">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="75">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="76">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="77">
+      <c r="I20" s="29"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="33"/>
+      <c r="X20" s="101">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="102">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="102">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="102">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="101">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="103">
         <v>1</v>
       </c>
       <c r="AD20" s="21" t="s">
@@ -3037,10 +3355,10 @@
       <c r="AL20" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="AM20" s="35" t="s">
+      <c r="AM20" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="AO20" s="34" t="s">
+      <c r="AO20" s="31" t="s">
         <v>40</v>
       </c>
       <c r="AP20" s="20" t="s">
@@ -3067,30 +3385,30 @@
       <c r="AW20" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="AX20" s="35" t="s">
+      <c r="AX20" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="AY20" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ20" s="58">
-        <v>1</v>
-      </c>
-      <c r="BA20" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB20" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC20" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD20" s="1">
+      <c r="AY20" s="141">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="141">
+        <v>1</v>
+      </c>
+      <c r="BA20" s="141">
+        <v>1</v>
+      </c>
+      <c r="BB20" s="141">
+        <v>0</v>
+      </c>
+      <c r="BC20" s="141">
+        <v>1</v>
+      </c>
+      <c r="BD20" s="142">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:56" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="50">
+      <c r="A21" s="45">
         <v>1</v>
       </c>
       <c r="B21" s="4">
@@ -3109,77 +3427,76 @@
         <v>1</v>
       </c>
       <c r="G21" s="6"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="37" t="s">
+      <c r="I21" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="38" t="s">
+      <c r="J21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="38" t="s">
+      <c r="K21" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L21" s="38" t="s">
+      <c r="L21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="M21" s="38" t="s">
+      <c r="M21" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="N21" s="38" t="s">
+      <c r="N21" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="O21" s="33" t="s">
+      <c r="O21" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="P21" s="38" t="s">
+      <c r="P21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="Q21" s="38" t="s">
+      <c r="Q21" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="R21" s="39" t="s">
+      <c r="R21" s="35" t="s">
         <v>26</v>
       </c>
       <c r="S21" s="7"/>
-      <c r="X21" s="86">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="87">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="87">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="73">
-        <v>0</v>
-      </c>
-      <c r="AY21" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ21" s="58">
-        <v>1</v>
-      </c>
-      <c r="BA21" s="4">
-        <v>1</v>
-      </c>
-      <c r="BB21" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC21" s="4">
-        <v>1</v>
-      </c>
-      <c r="BD21" s="5">
+      <c r="X21" s="106">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="107">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="107">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="107">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="106">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="108">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="143">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="143">
+        <v>1</v>
+      </c>
+      <c r="BA21" s="143">
+        <v>1</v>
+      </c>
+      <c r="BB21" s="143">
+        <v>1</v>
+      </c>
+      <c r="BC21" s="143">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="144">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="49">
+      <c r="A22" s="44">
         <v>1</v>
       </c>
       <c r="B22" s="2">
@@ -3198,59 +3515,58 @@
         <v>0</v>
       </c>
       <c r="G22" s="8"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="38" t="s">
+      <c r="J22" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K22" s="38" t="s">
+      <c r="K22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L22" s="38" t="s">
+      <c r="L22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="38" t="s">
+      <c r="M22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="38" t="s">
+      <c r="N22" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="O22" s="33" t="s">
+      <c r="O22" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="P22" s="38" t="s">
+      <c r="P22" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Q22" s="38" t="s">
+      <c r="Q22" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R22" s="39" t="s">
+      <c r="R22" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="X22" s="74">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="75">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="75">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="76">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="77">
+      <c r="X22" s="109">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="110">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="110">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="110">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="109">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="111">
         <v>1</v>
       </c>
       <c r="AD22" t="s">
         <v>53</v>
       </c>
-      <c r="AE22" s="55" t="s">
+      <c r="AE22" s="72" t="s">
         <v>54</v>
       </c>
       <c r="AF22" t="s">
@@ -3265,39 +3581,39 @@
       <c r="AO22" t="s">
         <v>53</v>
       </c>
-      <c r="AP22" s="55" t="s">
+      <c r="AP22" s="50" t="s">
         <v>54</v>
       </c>
       <c r="AQ22" t="s">
         <v>55</v>
       </c>
-      <c r="AR22" s="60" t="s">
+      <c r="AR22" s="54" t="s">
         <v>56</v>
       </c>
       <c r="AS22" t="s">
         <v>57</v>
       </c>
-      <c r="AY22" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ22" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA22" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB22" s="63">
-        <v>0</v>
-      </c>
-      <c r="BC22" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD22" s="1">
+      <c r="AY22" s="145">
+        <v>1</v>
+      </c>
+      <c r="AZ22" s="145">
+        <v>0</v>
+      </c>
+      <c r="BA22" s="145">
+        <v>0</v>
+      </c>
+      <c r="BB22" s="145">
+        <v>0</v>
+      </c>
+      <c r="BC22" s="145">
+        <v>0</v>
+      </c>
+      <c r="BD22" s="146">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A23" s="50">
+      <c r="A23" s="45">
         <v>1</v>
       </c>
       <c r="B23" s="4">
@@ -3316,88 +3632,85 @@
         <v>1</v>
       </c>
       <c r="G23" s="8"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38" t="s">
+      <c r="I23" s="36"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="30"/>
-      <c r="X23" s="86">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="87">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="87">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="73">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="85">
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="30"/>
+      <c r="R23" s="27"/>
+      <c r="X23" s="112">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="113">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="113">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="113">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="112">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="114">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="65">
         <v>9</v>
       </c>
-      <c r="AE23" s="56">
+      <c r="AE23" s="73">
         <v>5</v>
       </c>
-      <c r="AF23" s="54">
+      <c r="AF23" s="49">
         <v>8</v>
       </c>
-      <c r="AG23" s="54">
+      <c r="AG23" s="49">
         <v>7</v>
       </c>
-      <c r="AH23" s="54">
+      <c r="AH23" s="49">
         <v>8</v>
       </c>
-      <c r="AO23" s="54">
+      <c r="AO23" s="49">
         <v>9</v>
       </c>
-      <c r="AP23" s="56">
+      <c r="AP23" s="51">
         <v>5</v>
       </c>
-      <c r="AQ23" s="54">
+      <c r="AQ23" s="49">
         <v>8</v>
       </c>
-      <c r="AR23" s="61">
+      <c r="AR23" s="55">
         <v>7</v>
       </c>
-      <c r="AS23" s="54">
+      <c r="AS23" s="49">
         <v>8</v>
       </c>
-      <c r="AY23" s="4">
-        <v>1</v>
-      </c>
-      <c r="AZ23" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA23" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB23" s="63">
-        <v>0</v>
-      </c>
-      <c r="BC23" s="4">
-        <v>1</v>
-      </c>
-      <c r="BD23" s="5">
+      <c r="AY23" s="147">
+        <v>1</v>
+      </c>
+      <c r="AZ23" s="147">
+        <v>0</v>
+      </c>
+      <c r="BA23" s="147">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="147">
+        <v>1</v>
+      </c>
+      <c r="BC23" s="147">
+        <v>0</v>
+      </c>
+      <c r="BD23" s="148">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="50">
+      <c r="A24" s="45">
         <v>1</v>
       </c>
       <c r="B24" s="4">
@@ -3416,58 +3729,55 @@
         <v>1</v>
       </c>
       <c r="G24" s="8"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38" t="s">
+      <c r="I24" s="36"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="30"/>
-      <c r="X24" s="74">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="75">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="75">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="76">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="77">
-        <v>1</v>
-      </c>
-      <c r="AY24" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ24" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA24" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB24" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC24" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD24" s="1">
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="30"/>
+      <c r="R24" s="27"/>
+      <c r="X24" s="115">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="116">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="116">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="116">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="115">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="117">
+        <v>1</v>
+      </c>
+      <c r="AY24" s="149">
+        <v>1</v>
+      </c>
+      <c r="AZ24" s="149">
+        <v>0</v>
+      </c>
+      <c r="BA24" s="149">
+        <v>1</v>
+      </c>
+      <c r="BB24" s="149">
+        <v>0</v>
+      </c>
+      <c r="BC24" s="149">
+        <v>0</v>
+      </c>
+      <c r="BD24" s="150">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A25" s="49">
+      <c r="A25" s="44">
         <v>1</v>
       </c>
       <c r="B25" s="2">
@@ -3486,56 +3796,57 @@
         <v>0</v>
       </c>
       <c r="G25" s="8"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="30"/>
-      <c r="X25" s="78">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="79">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="79">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="79">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="80">
-        <v>1</v>
-      </c>
-      <c r="AY25" s="4">
-        <v>1</v>
-      </c>
-      <c r="AZ25" s="58">
-        <v>0</v>
-      </c>
-      <c r="BA25" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB25" s="63">
-        <v>1</v>
-      </c>
-      <c r="BC25" s="4">
-        <v>1</v>
-      </c>
-      <c r="BD25" s="5">
+      <c r="I25" s="36"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="30"/>
+      <c r="R25" s="27"/>
+      <c r="X25" s="118">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="119">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="119">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="119">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="118">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="120">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="104" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG25" s="104"/>
+      <c r="AY25" s="151">
+        <v>1</v>
+      </c>
+      <c r="AZ25" s="151">
+        <v>0</v>
+      </c>
+      <c r="BA25" s="151">
+        <v>1</v>
+      </c>
+      <c r="BB25" s="151">
+        <v>1</v>
+      </c>
+      <c r="BC25" s="151">
+        <v>0</v>
+      </c>
+      <c r="BD25" s="152">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="50">
+      <c r="A26" s="45">
         <v>1</v>
       </c>
       <c r="B26" s="4">
@@ -3554,65 +3865,57 @@
         <v>1</v>
       </c>
       <c r="G26" s="8"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="30"/>
-      <c r="X26" s="88">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="89">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="89">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="89">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="76">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="81">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="64" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG26" s="84" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH26" s="64" t="s">
-        <v>63</v>
-      </c>
-      <c r="AT26" s="4">
-        <v>1</v>
-      </c>
-      <c r="AU26" s="58">
-        <v>0</v>
-      </c>
-      <c r="AV26" s="4">
-        <v>1</v>
-      </c>
-      <c r="AW26" s="63">
-        <v>0</v>
-      </c>
-      <c r="AX26" s="4">
-        <v>0</v>
-      </c>
-      <c r="AY26" s="5">
+      <c r="I26" s="36"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="30"/>
+      <c r="R26" s="27"/>
+      <c r="X26" s="121">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="122">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="122">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="122">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="121">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="123">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="104" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG26" s="104"/>
+      <c r="AY26" s="153">
+        <v>1</v>
+      </c>
+      <c r="AZ26" s="153">
+        <v>1</v>
+      </c>
+      <c r="BA26" s="153">
+        <v>0</v>
+      </c>
+      <c r="BB26" s="153">
+        <v>0</v>
+      </c>
+      <c r="BC26" s="153">
+        <v>0</v>
+      </c>
+      <c r="BD26" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A27" s="49">
+      <c r="A27" s="44">
         <v>1</v>
       </c>
       <c r="B27" s="2">
@@ -3630,62 +3933,58 @@
       <c r="F27" s="1">
         <v>0</v>
       </c>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="30"/>
-      <c r="X27" s="78">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="79">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="79">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="79">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="72">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="80">
-        <v>1</v>
-      </c>
-      <c r="AF27" s="69" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG27" s="69"/>
-      <c r="AH27" s="68"/>
-      <c r="AT27" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU27" s="58">
-        <v>0</v>
-      </c>
-      <c r="AV27" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW27" s="63">
-        <v>0</v>
-      </c>
-      <c r="AX27" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY27" s="1">
+      <c r="I27" s="36"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="R27" s="27"/>
+      <c r="X27" s="124">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="125">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="125">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="125">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="124">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="126">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="105" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG27" s="105"/>
+      <c r="AH27" s="90"/>
+      <c r="AY27" s="154">
+        <v>1</v>
+      </c>
+      <c r="AZ27" s="154">
+        <v>1</v>
+      </c>
+      <c r="BA27" s="154">
+        <v>0</v>
+      </c>
+      <c r="BB27" s="154">
+        <v>1</v>
+      </c>
+      <c r="BC27" s="154">
+        <v>0</v>
+      </c>
+      <c r="BD27" s="155">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="49">
+      <c r="A28" s="44">
         <v>1</v>
       </c>
       <c r="B28" s="2">
@@ -3703,60 +4002,58 @@
       <c r="F28" s="1">
         <v>0</v>
       </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="30"/>
-      <c r="X28" s="88">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="89">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="89">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="89">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="76">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="81">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="69"/>
-      <c r="AG28" s="68"/>
-      <c r="AH28" s="68"/>
-      <c r="AT28" s="4">
-        <v>1</v>
-      </c>
-      <c r="AU28" s="58">
-        <v>0</v>
-      </c>
-      <c r="AV28" s="4">
-        <v>1</v>
-      </c>
-      <c r="AW28" s="63">
-        <v>1</v>
-      </c>
-      <c r="AX28" s="4">
-        <v>0</v>
-      </c>
-      <c r="AY28" s="5">
+      <c r="I28" s="36"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="R28" s="27"/>
+      <c r="X28" s="127">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="128">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="128">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="128">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="127">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="129">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG28" s="104"/>
+      <c r="AH28" s="91"/>
+      <c r="AY28" s="156">
+        <v>1</v>
+      </c>
+      <c r="AZ28" s="156">
+        <v>1</v>
+      </c>
+      <c r="BA28" s="156">
+        <v>1</v>
+      </c>
+      <c r="BB28" s="156">
+        <v>0</v>
+      </c>
+      <c r="BC28" s="156">
+        <v>0</v>
+      </c>
+      <c r="BD28" s="157">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A29" s="50">
+      <c r="A29" s="45">
         <v>1</v>
       </c>
       <c r="B29" s="4">
@@ -3774,60 +4071,67 @@
       <c r="F29" s="5">
         <v>1</v>
       </c>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="30"/>
-      <c r="X29" s="86">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="87">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="87">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="72">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="73">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="69"/>
-      <c r="AG29" s="68"/>
-      <c r="AH29" s="68"/>
-      <c r="AT29" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU29" s="58">
-        <v>0</v>
-      </c>
-      <c r="AV29" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW29" s="63">
-        <v>1</v>
-      </c>
-      <c r="AX29" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY29" s="1">
+      <c r="I29" s="29"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="R29" s="27"/>
+      <c r="X29" s="106">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="107">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="107">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="107">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="106">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="108">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG29" s="104"/>
+      <c r="AH29" s="91"/>
+      <c r="AS29" s="134" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT29" s="134" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU29" s="134" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY29" s="130">
+        <v>1</v>
+      </c>
+      <c r="AZ29" s="130">
+        <v>1</v>
+      </c>
+      <c r="BA29" s="130">
+        <v>1</v>
+      </c>
+      <c r="BB29" s="130">
+        <v>1</v>
+      </c>
+      <c r="BC29" s="130">
+        <v>0</v>
+      </c>
+      <c r="BD29" s="42">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="50">
+    <row r="30" spans="1:56" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="45">
         <v>1</v>
       </c>
       <c r="B30" s="4">
@@ -3845,64 +4149,74 @@
       <c r="F30" s="5">
         <v>1</v>
       </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="31" t="s">
+      <c r="I30" s="28" t="s">
         <v>32</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="30"/>
-      <c r="X30" s="74">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="75">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="75">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="76">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="77">
-        <v>1</v>
-      </c>
-      <c r="AF30" s="69"/>
-      <c r="AG30" s="68"/>
-      <c r="AH30" s="68"/>
-      <c r="AT30" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU30" s="58">
-        <v>1</v>
-      </c>
-      <c r="AV30" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW30" s="63">
-        <v>0</v>
-      </c>
-      <c r="AX30" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY30" s="1">
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="R30" s="27"/>
+      <c r="X30" s="109">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="110">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="110">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="110">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="109">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="111">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="104" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG30" s="104"/>
+      <c r="AH30" s="91"/>
+      <c r="AS30" s="135" t="s">
+        <v>62</v>
+      </c>
+      <c r="AT30" s="136" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU30" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>110</v>
+      </c>
+      <c r="AY30" s="145">
+        <v>1</v>
+      </c>
+      <c r="AZ30" s="145">
+        <v>0</v>
+      </c>
+      <c r="BA30" s="145">
+        <v>0</v>
+      </c>
+      <c r="BB30" s="145">
+        <v>0</v>
+      </c>
+      <c r="BC30" s="145">
+        <v>1</v>
+      </c>
+      <c r="BD30" s="146">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:56" x14ac:dyDescent="0.2">
-      <c r="A31" s="49">
+    <row r="31" spans="1:56" ht="34" x14ac:dyDescent="0.2">
+      <c r="A31" s="44">
         <v>1</v>
       </c>
       <c r="B31" s="2">
@@ -3920,64 +4234,74 @@
       <c r="F31" s="1">
         <v>0</v>
       </c>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="31" t="s">
+      <c r="I31" s="28" t="s">
         <v>33</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="30"/>
-      <c r="X31" s="78">
-        <v>1</v>
-      </c>
-      <c r="Y31" s="79">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="79">
-        <v>1</v>
-      </c>
-      <c r="AA31" s="79">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="72">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="80">
-        <v>1</v>
-      </c>
-      <c r="AF31" s="69"/>
-      <c r="AG31" s="68"/>
-      <c r="AH31" s="68"/>
-      <c r="AT31" s="4">
-        <v>1</v>
-      </c>
-      <c r="AU31" s="58">
-        <v>1</v>
-      </c>
-      <c r="AV31" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW31" s="63">
-        <v>0</v>
-      </c>
-      <c r="AX31" s="4">
-        <v>1</v>
-      </c>
-      <c r="AY31" s="5">
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="R31" s="27"/>
+      <c r="X31" s="112">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="113">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="113">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="113">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="112">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="114">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="91" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG31" s="91"/>
+      <c r="AH31" s="91"/>
+      <c r="AS31" s="135" t="s">
+        <v>89</v>
+      </c>
+      <c r="AT31" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU31" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY31" s="147">
+        <v>1</v>
+      </c>
+      <c r="AZ31" s="147">
+        <v>0</v>
+      </c>
+      <c r="BA31" s="147">
+        <v>0</v>
+      </c>
+      <c r="BB31" s="147">
+        <v>1</v>
+      </c>
+      <c r="BC31" s="147">
+        <v>1</v>
+      </c>
+      <c r="BD31" s="148">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:56" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="50">
+    <row r="32" spans="1:56" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="45">
         <v>1</v>
       </c>
       <c r="B32" s="4">
@@ -3995,64 +4319,72 @@
       <c r="F32" s="5">
         <v>1</v>
       </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="31" t="s">
+      <c r="I32" s="28" t="s">
         <v>34</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="30"/>
-      <c r="X32" s="88">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="89">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="89">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="89">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="76">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="81">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="69"/>
-      <c r="AG32" s="68"/>
-      <c r="AH32" s="68"/>
-      <c r="AT32" s="4">
-        <v>1</v>
-      </c>
-      <c r="AU32" s="58">
-        <v>1</v>
-      </c>
-      <c r="AV32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW32" s="63">
-        <v>1</v>
-      </c>
-      <c r="AX32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AY32" s="5">
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="R32" s="27"/>
+      <c r="X32" s="115">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="116">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="116">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="116">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="115">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="117">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="91" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS32" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="AT32" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU32" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>112</v>
+      </c>
+      <c r="AY32" s="149">
+        <v>1</v>
+      </c>
+      <c r="AZ32" s="149">
+        <v>0</v>
+      </c>
+      <c r="BA32" s="149">
+        <v>1</v>
+      </c>
+      <c r="BB32" s="149">
+        <v>0</v>
+      </c>
+      <c r="BC32" s="149">
+        <v>1</v>
+      </c>
+      <c r="BD32" s="150">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="A33" s="50">
+    <row r="33" spans="1:56" ht="34" x14ac:dyDescent="0.2">
+      <c r="A33" s="45">
         <v>1</v>
       </c>
       <c r="B33" s="4">
@@ -4070,64 +4402,69 @@
       <c r="F33" s="5">
         <v>1</v>
       </c>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="31" t="s">
+      <c r="I33" s="28" t="s">
         <v>35</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="30"/>
-      <c r="X33" s="78">
-        <v>1</v>
-      </c>
-      <c r="Y33" s="79">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="79">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="79">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="72">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="80">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="69"/>
-      <c r="AG33" s="68"/>
-      <c r="AH33" s="68"/>
-      <c r="AT33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU33" s="58">
-        <v>1</v>
-      </c>
-      <c r="AV33" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW33" s="63">
-        <v>1</v>
-      </c>
-      <c r="AX33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY33" s="1">
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="R33" s="27"/>
+      <c r="X33" s="118">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="119">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="119">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="119">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="118">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="120">
+        <v>1</v>
+      </c>
+      <c r="AS33" s="135" t="s">
+        <v>92</v>
+      </c>
+      <c r="AT33" s="136" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU33" s="135" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV33" t="s">
+        <v>113</v>
+      </c>
+      <c r="AY33" s="151">
+        <v>1</v>
+      </c>
+      <c r="AZ33" s="151">
+        <v>0</v>
+      </c>
+      <c r="BA33" s="151">
+        <v>1</v>
+      </c>
+      <c r="BB33" s="151">
+        <v>1</v>
+      </c>
+      <c r="BC33" s="151">
+        <v>1</v>
+      </c>
+      <c r="BD33" s="152">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:51" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="49">
+    <row r="34" spans="1:56" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="44">
         <v>1</v>
       </c>
       <c r="B34" s="2">
@@ -4145,217 +4482,422 @@
       <c r="F34" s="1">
         <v>0</v>
       </c>
-      <c r="G34" s="29"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="30"/>
-      <c r="X34" s="74">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="75">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="75">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="75">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="76">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="77">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="69"/>
-      <c r="AG34" s="68"/>
-      <c r="AH34" s="68"/>
-      <c r="AT34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AU34" s="58">
-        <v>1</v>
-      </c>
-      <c r="AV34" s="4">
-        <v>1</v>
-      </c>
-      <c r="AW34" s="63">
-        <v>0</v>
-      </c>
-      <c r="AX34" s="4">
-        <v>0</v>
-      </c>
-      <c r="AY34" s="5">
+      <c r="H34" s="30"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="R34" s="27"/>
+      <c r="X34" s="121">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="122">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="122">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="122">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="121">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="123">
+        <v>1</v>
+      </c>
+      <c r="AS34" s="135" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT34" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU34" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>114</v>
+      </c>
+      <c r="AY34" s="153">
+        <v>1</v>
+      </c>
+      <c r="AZ34" s="153">
+        <v>1</v>
+      </c>
+      <c r="BA34" s="153">
+        <v>0</v>
+      </c>
+      <c r="BB34" s="153">
+        <v>0</v>
+      </c>
+      <c r="BC34" s="153">
+        <v>1</v>
+      </c>
+      <c r="BD34" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:51" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="51">
-        <v>1</v>
-      </c>
-      <c r="B35" s="52">
-        <v>1</v>
-      </c>
-      <c r="C35" s="52">
-        <v>1</v>
-      </c>
-      <c r="D35" s="52">
-        <v>1</v>
-      </c>
-      <c r="E35" s="52">
-        <v>1</v>
-      </c>
-      <c r="F35" s="53">
-        <v>0</v>
-      </c>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="42"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="43"/>
-      <c r="X35" s="86">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="87">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="87">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="72">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="73">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="69"/>
-      <c r="AG35" s="68"/>
-      <c r="AH35" s="68"/>
-      <c r="AT35" s="4">
-        <v>1</v>
-      </c>
-      <c r="AU35" s="58">
-        <v>1</v>
-      </c>
-      <c r="AV35" s="4">
-        <v>1</v>
-      </c>
-      <c r="AW35" s="63">
-        <v>0</v>
-      </c>
-      <c r="AX35" s="4">
-        <v>1</v>
-      </c>
-      <c r="AY35" s="5">
+    <row r="35" spans="1:56" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="46">
+        <v>1</v>
+      </c>
+      <c r="B35" s="47">
+        <v>1</v>
+      </c>
+      <c r="C35" s="47">
+        <v>1</v>
+      </c>
+      <c r="D35" s="47">
+        <v>1</v>
+      </c>
+      <c r="E35" s="47">
+        <v>1</v>
+      </c>
+      <c r="F35" s="48">
+        <v>0</v>
+      </c>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="39"/>
+      <c r="X35" s="124">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="125">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="125">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="125">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="124">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="126">
+        <v>0</v>
+      </c>
+      <c r="AS35" s="135" t="s">
+        <v>95</v>
+      </c>
+      <c r="AT35" s="136" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU35" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="AV35" t="s">
+        <v>115</v>
+      </c>
+      <c r="AY35" s="154">
+        <v>1</v>
+      </c>
+      <c r="AZ35" s="154">
+        <v>1</v>
+      </c>
+      <c r="BA35" s="154">
+        <v>0</v>
+      </c>
+      <c r="BB35" s="154">
+        <v>1</v>
+      </c>
+      <c r="BC35" s="154">
+        <v>1</v>
+      </c>
+      <c r="BD35" s="155">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:51" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="X36" s="88">
-        <v>1</v>
-      </c>
-      <c r="Y36" s="89">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="89">
-        <v>1</v>
-      </c>
-      <c r="AA36" s="89">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="76">
-        <v>1</v>
-      </c>
-      <c r="AC36" s="81">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="69"/>
-      <c r="AG36" s="68"/>
-      <c r="AH36" s="68"/>
-      <c r="AT36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU36" s="58">
-        <v>1</v>
-      </c>
-      <c r="AV36" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW36" s="63">
-        <v>1</v>
-      </c>
-      <c r="AX36" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY36" s="1">
+    <row r="36" spans="1:56" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="X36" s="127">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="128">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="128">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="128">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="127">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="129">
+        <v>0</v>
+      </c>
+      <c r="AS36" s="135" t="s">
+        <v>96</v>
+      </c>
+      <c r="AT36" s="136" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU36" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="AV36" t="s">
+        <v>116</v>
+      </c>
+      <c r="AY36" s="156">
+        <v>1</v>
+      </c>
+      <c r="AZ36" s="156">
+        <v>1</v>
+      </c>
+      <c r="BA36" s="156">
+        <v>1</v>
+      </c>
+      <c r="BB36" s="156">
+        <v>0</v>
+      </c>
+      <c r="BC36" s="156">
+        <v>1</v>
+      </c>
+      <c r="BD36" s="157">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="AF37" s="69"/>
-      <c r="AG37" s="68"/>
-      <c r="AH37" s="68"/>
-      <c r="AT37" s="2">
-        <v>1</v>
-      </c>
-      <c r="AU37" s="58">
-        <v>1</v>
-      </c>
-      <c r="AV37" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW37" s="63">
-        <v>1</v>
-      </c>
-      <c r="AX37" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY37" s="1">
+    <row r="37" spans="1:56" ht="34" x14ac:dyDescent="0.2">
+      <c r="AS37" s="135" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT37" s="136" t="s">
+        <v>98</v>
+      </c>
+      <c r="AU37" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV37" t="s">
+        <v>117</v>
+      </c>
+      <c r="AY37" s="130">
+        <v>1</v>
+      </c>
+      <c r="AZ37" s="130">
+        <v>1</v>
+      </c>
+      <c r="BA37" s="130">
+        <v>1</v>
+      </c>
+      <c r="BB37" s="130">
+        <v>1</v>
+      </c>
+      <c r="BC37" s="130">
+        <v>1</v>
+      </c>
+      <c r="BD37" s="42">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="AF38" s="69"/>
-      <c r="AG38" s="68"/>
-      <c r="AH38" s="68"/>
+    <row r="38" spans="1:56" ht="34" x14ac:dyDescent="0.2">
+      <c r="AF38" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG38" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH38" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS38" s="135" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT38" s="136" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU38" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="AV38" t="s">
+        <v>118</v>
+      </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="AF39" s="69"/>
-      <c r="AG39" s="68"/>
-      <c r="AH39" s="68"/>
+    <row r="39" spans="1:56" ht="68" x14ac:dyDescent="0.2">
+      <c r="AF39" s="84" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG39" s="85" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH39" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS39" s="135" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT39" s="136" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU39" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV39" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="AF40" s="69"/>
-      <c r="AG40" s="68"/>
-      <c r="AH40" s="68"/>
+    <row r="40" spans="1:56" ht="68" x14ac:dyDescent="0.2">
+      <c r="AF40" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG40" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH40" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS40" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT40" s="136" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU40" s="135" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="s">
+        <v>120</v>
+      </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="AF41" s="69"/>
-      <c r="AG41" s="68"/>
-      <c r="AH41" s="68"/>
+    <row r="41" spans="1:56" ht="68" x14ac:dyDescent="0.2">
+      <c r="AF41" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG41" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH41" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS41" s="135" t="s">
+        <v>103</v>
+      </c>
+      <c r="AT41" s="136" t="s">
+        <v>104</v>
+      </c>
+      <c r="AU41" s="135" t="s">
+        <v>105</v>
+      </c>
+      <c r="AV41" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="AF42" s="69"/>
-      <c r="AG42" s="68"/>
-      <c r="AH42" s="68"/>
+    <row r="42" spans="1:56" ht="68" x14ac:dyDescent="0.2">
+      <c r="AF42" s="84" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG42" s="85" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH42" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS42" s="135" t="s">
+        <v>106</v>
+      </c>
+      <c r="AT42" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU42" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV42" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:56" ht="68" x14ac:dyDescent="0.2">
+      <c r="AF43" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG43" s="85" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH43" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS43" s="135" t="s">
+        <v>107</v>
+      </c>
+      <c r="AT43" s="136" t="s">
+        <v>93</v>
+      </c>
+      <c r="AU43" s="135" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV43" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:56" ht="68" x14ac:dyDescent="0.2">
+      <c r="AF44" s="84" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG44" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH44" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS44" s="135" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT44" s="136" t="s">
+        <v>104</v>
+      </c>
+      <c r="AU44" s="135" t="s">
+        <v>105</v>
+      </c>
+      <c r="AV44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:56" ht="68" x14ac:dyDescent="0.2">
+      <c r="AF45" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG45" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH45" s="84" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS45" s="135" t="s">
+        <v>109</v>
+      </c>
+      <c r="AT45" s="136" t="s">
+        <v>88</v>
+      </c>
+      <c r="AU45" s="135" t="s">
+        <v>59</v>
+      </c>
+      <c r="AV45" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:56" ht="68" x14ac:dyDescent="0.2">
+      <c r="AF46" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG46" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH46" s="84" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS46" s="133"/>
+      <c r="AT46" s="133"/>
+      <c r="AU46" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4365,6 +4907,7 @@
     <mergeCell ref="AQ12:AT12"/>
     <mergeCell ref="AF12:AI12"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/labs/4.lab/4.lab.xlsx
+++ b/labs/4.lab/4.lab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rod/Documents/ehu/dt/labs/4.lab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B746B8-A40A-3E46-A2AE-A15A95B00E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F9029E-A0D7-1C4C-9F8B-9CBA5F385C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="0" windowWidth="21440" windowHeight="22400" xr2:uid="{B4FD20D9-57F3-4747-AA10-0A42781B4A42}"/>
   </bookViews>
